--- a/example6-rppa/input/comparisons.xlsx
+++ b/example6-rppa/input/comparisons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanmaygandhi/Box Sync/runModac/example6-rppa/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C1255E-9946-4B4A-9129-D3A0E9177A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F18CF8-1414-C642-9E5E-F6CFE6C95E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76180" yWindow="3240" windowWidth="19520" windowHeight="17320" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{AC62268A-3574-A143-9B0A-533FA44997D6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="6" r:id="rId1"/>
@@ -52,12 +52,6 @@
     <t>comparison_name</t>
   </si>
   <si>
-    <t>group_order_ctrl_test</t>
-  </si>
-  <si>
-    <t>statistic_selector</t>
-  </si>
-  <si>
     <t>QC_row</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>ISTD_column</t>
   </si>
   <si>
-    <t>statistic_cutoff</t>
-  </si>
-  <si>
     <t>none</t>
   </si>
   <si>
@@ -119,6 +110,15 @@
   </si>
   <si>
     <t>pval</t>
+  </si>
+  <si>
+    <t>padj_method</t>
+  </si>
+  <si>
+    <t>padj_cutoff</t>
+  </si>
+  <si>
+    <t>group_order</t>
   </si>
 </sst>
 </file>
@@ -610,15 +610,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>0.05</v>
@@ -626,15 +626,15 @@
     </row>
     <row r="3" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="5" spans="1:2" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>41</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="6" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>0.25</v>
@@ -658,15 +658,15 @@
     </row>
     <row r="7" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
@@ -674,10 +674,10 @@
     </row>
     <row r="9" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -701,7 +701,7 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -714,13 +714,13 @@
     </row>
     <row r="3" spans="1:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -734,50 +734,50 @@
     </row>
     <row r="5" spans="1:4" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
